--- a/results/log_pv_cap_per_inst/log_pv_cap_per_inst_baseline_tests.xlsx
+++ b/results/log_pv_cap_per_inst/log_pv_cap_per_inst_baseline_tests.xlsx
@@ -451,27 +451,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81.84***</t>
+          <t>84.15***</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.07***</t>
+          <t>12.95***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6763.19***</t>
+          <t>7248.77***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.51***</t>
+          <t>81.78***</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.48***</t>
+          <t>79.53***</t>
         </is>
       </c>
     </row>
@@ -483,27 +483,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.84***</t>
+          <t>84.15***</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.74***</t>
+          <t>4.28***</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6712.02***</t>
+          <t>7099.36***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.82***</t>
+          <t>20.47***</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.48***</t>
+          <t>79.53***</t>
         </is>
       </c>
     </row>
@@ -515,27 +515,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>81.84***</t>
+          <t>84.15***</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.34***</t>
+          <t>4.53***</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6716.85***</t>
+          <t>7101.55***</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.73***</t>
+          <t>14.60***</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.48***</t>
+          <t>79.53***</t>
         </is>
       </c>
     </row>
